--- a/data/trans_camb/IP41-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP41-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 4,01</t>
+          <t>-5,53; 3,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,71; -0,85</t>
+          <t>-12,07; -0,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-97,62; -90,0</t>
+          <t>-97,62; -90,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 4,93</t>
+          <t>-5,87; 5,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 1,66</t>
+          <t>-9,31; 2,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-95,0; -86,84</t>
+          <t>-95,13; -87,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 3,11</t>
+          <t>-4,1; 2,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,73; -0,69</t>
+          <t>-9,23; -0,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-95,76; -90,55</t>
+          <t>-95,55; -90,13</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 4,34</t>
+          <t>-5,69; 4,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,12; -1,11</t>
+          <t>-12,47; -0,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 5,57</t>
+          <t>-6,23; 5,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 1,87</t>
+          <t>-10,09; 2,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 3,4</t>
+          <t>-4,28; 3,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,3; -0,76</t>
+          <t>-9,75; -0,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 1,69</t>
+          <t>-7,55; 1,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 0,77</t>
+          <t>-8,61; 0,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-93,39; -87,37</t>
+          <t>-93,54; -87,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 0,83</t>
+          <t>-7,61; 0,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,67; -5,51</t>
+          <t>-14,43; -5,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-95,33; -89,98</t>
+          <t>-95,41; -90,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,41; -0,15</t>
+          <t>-6,13; -0,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,49; -3,92</t>
+          <t>-10,53; -4,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-93,74; -89,8</t>
+          <t>-93,53; -89,64</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 1,94</t>
+          <t>-8,31; 1,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 0,89</t>
+          <t>-9,28; 0,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 0,77</t>
+          <t>-8,08; 0,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,49; -5,98</t>
+          <t>-15,43; -6,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,9; -0,17</t>
+          <t>-6,61; -0,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,21; -4,3</t>
+          <t>-11,44; -4,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 9,54</t>
+          <t>-3,48; 9,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 0,91</t>
+          <t>-13,05; 1,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-89,68; -79,37</t>
+          <t>-89,97; -79,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 1,52</t>
+          <t>-9,62; 1,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,35; -5,18</t>
+          <t>-16,79; -4,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-95,38; -88,17</t>
+          <t>-95,2; -87,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 3,41</t>
+          <t>-4,6; 3,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,26; -3,98</t>
+          <t>-13,3; -4,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-91,7; -85,66</t>
+          <t>-91,72; -85,58</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 11,77</t>
+          <t>-3,93; 12,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 1,34</t>
+          <t>-14,73; 1,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 1,64</t>
+          <t>-10,21; 1,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,36; -5,74</t>
+          <t>-18,04; -5,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 3,96</t>
+          <t>-5,02; 4,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-14,64; -4,62</t>
+          <t>-14,66; -4,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,37; -0,42</t>
+          <t>-10,7; -0,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,82; -4,82</t>
+          <t>-16,3; -4,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-95,65; -89,28</t>
+          <t>-95,71; -89,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,0; -3,06</t>
+          <t>-13,13; -2,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,7; -3,11</t>
+          <t>-14,27; -2,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-94,8; -88,78</t>
+          <t>-94,65; -88,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,57; -3,22</t>
+          <t>-10,63; -3,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-14,0; -5,39</t>
+          <t>-13,49; -5,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-94,64; -90,51</t>
+          <t>-94,57; -90,42</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,99; -0,49</t>
+          <t>-11,36; -0,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,72; -5,28</t>
+          <t>-17,32; -4,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,06; -3,38</t>
+          <t>-14,06; -3,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,79; -3,45</t>
+          <t>-15,11; -3,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,41; -3,54</t>
+          <t>-11,4; -3,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,88; -5,9</t>
+          <t>-14,34; -5,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,7</t>
+          <t>-4,45; 0,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,74; -3,9</t>
+          <t>-10,16; -4,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-92,76; -89,19</t>
+          <t>-92,77; -89,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,73; -1,64</t>
+          <t>-6,67; -1,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,34; -5,66</t>
+          <t>-11,36; -5,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-93,89; -90,54</t>
+          <t>-93,81; -90,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -1,49</t>
+          <t>-4,98; -1,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,82; -5,87</t>
+          <t>-9,73; -5,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-92,95; -90,5</t>
+          <t>-92,92; -90,55</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,77</t>
+          <t>-4,85; 0,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,58; -4,37</t>
+          <t>-11,04; -4,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,27; -1,83</t>
+          <t>-7,12; -1,88</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-12,22; -6,19</t>
+          <t>-12,27; -6,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,4; -1,64</t>
+          <t>-5,36; -1,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,64; -6,43</t>
+          <t>-10,44; -6,47</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">

--- a/data/trans_camb/IP41-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP41-Edad-trans_camb.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -63,13 +63,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -504,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +508,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,21 +523,18 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -564,37 +551,22 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2012/2007</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>2016/2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>2012/2007</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
         </is>
       </c>
     </row>
@@ -607,9 +579,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -634,37 +603,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-94,97</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-3,69</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-3,69</t>
+          <t>-0,62</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-91,78</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-0,62</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
           <t>-4,86</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-93,26</t>
         </is>
       </c>
     </row>
@@ -677,47 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 3,84</t>
+          <t>-5,09; 3,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,07; -0,72</t>
+          <t>-11,84; -0,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-97,62; -90,37</t>
+          <t>-5,94; 5,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 5,08</t>
+          <t>-9,57; 2,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 2,71</t>
+          <t>-3,83; 3,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-95,13; -87,05</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-4,1; 2,94</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-9,23; -0,69</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-95,55; -90,13</t>
+          <t>-9,3; -0,71</t>
         </is>
       </c>
     </row>
@@ -740,37 +679,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-0,6%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,6%</t>
+          <t>-4,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-4,02%</t>
+          <t>-0,67%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-0,67%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
           <t>-5,21%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -783,47 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 4,18</t>
+          <t>-5,28; 3,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,47; -0,85</t>
+          <t>-12,26; -1,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,36; 5,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 5,72</t>
+          <t>-10,25; 2,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 2,8</t>
+          <t>-4,04; 3,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-4,28; 3,18</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-9,75; -0,88</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-9,75; -0,81</t>
         </is>
       </c>
     </row>
@@ -850,37 +759,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-90,72</t>
+          <t>-3,62</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,62</t>
+          <t>-9,71</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-9,71</t>
+          <t>-3,23</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-92,98</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-3,23</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
           <t>-7,08</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-91,85</t>
         </is>
       </c>
     </row>
@@ -893,47 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 1,21</t>
+          <t>-7,63; 1,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 0,88</t>
+          <t>-9,42; 0,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-93,54; -87,13</t>
+          <t>-7,59; 0,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 0,55</t>
+          <t>-14,37; -4,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,43; -5,33</t>
+          <t>-6,22; -0,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-95,41; -90,1</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-6,13; -0,19</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-10,53; -4,0</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-93,53; -89,64</t>
+          <t>-10,6; -3,8</t>
         </is>
       </c>
     </row>
@@ -956,37 +835,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-3,9%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,9%</t>
+          <t>-10,44%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-10,44%</t>
+          <t>-3,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-3,52%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
           <t>-7,71%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 1,32</t>
+          <t>-8,32; 2,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 0,95</t>
+          <t>-10,26; 0,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,21; 0,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 0,59</t>
+          <t>-15,15; -5,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,43; -6,0</t>
+          <t>-6,71; -0,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-6,61; -0,21</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-11,44; -4,46</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-11,28; -4,16</t>
         </is>
       </c>
     </row>
@@ -1066,37 +915,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-85,34</t>
+          <t>-3,51</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,51</t>
+          <t>-10,64</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-10,64</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-92,27</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
           <t>-8,46</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>-88,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 9,87</t>
+          <t>-3,32; 10,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 1,63</t>
+          <t>-12,96; 1,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-89,97; -79,46</t>
+          <t>-9,21; 2,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 1,81</t>
+          <t>-16,6; -4,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,79; -4,5</t>
+          <t>-4,83; 3,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-95,2; -87,7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-4,6; 3,97</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-13,3; -4,0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-91,72; -85,58</t>
+          <t>-12,95; -3,82</t>
         </is>
       </c>
     </row>
@@ -1172,37 +991,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-3,8%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,8%</t>
+          <t>-11,54%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-11,54%</t>
+          <t>-0,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-0,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
           <t>-9,51%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 12,12</t>
+          <t>-3,74; 13,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 1,99</t>
+          <t>-14,68; 1,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,76; 2,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 1,91</t>
+          <t>-17,61; -5,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,04; -5,11</t>
+          <t>-5,3; 4,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-5,02; 4,62</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-14,66; -4,64</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-14,3; -4,54</t>
         </is>
       </c>
     </row>
@@ -1282,37 +1071,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-93,24</t>
+          <t>-8,21</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-8,21</t>
+          <t>-8,4</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-8,4</t>
+          <t>-6,82</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-92,08</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-6,82</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
           <t>-9,3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>-92,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,7; -0,49</t>
+          <t>-10,65; -0,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,3; -4,64</t>
+          <t>-15,73; -4,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-95,71; -89,78</t>
+          <t>-13,85; -3,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,13; -2,75</t>
+          <t>-14,01; -3,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,27; -2,94</t>
+          <t>-10,6; -3,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-94,65; -88,33</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-10,63; -3,11</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-13,49; -5,27</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-94,57; -90,42</t>
+          <t>-13,37; -5,28</t>
         </is>
       </c>
     </row>
@@ -1388,37 +1147,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-8,92%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-8,92%</t>
+          <t>-9,13%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-9,13%</t>
+          <t>-7,36%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-7,36%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
           <t>-10,03%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,36; -0,55</t>
+          <t>-11,25; -0,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,32; -4,99</t>
+          <t>-16,51; -4,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,86; -3,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,06; -3,1</t>
+          <t>-15,07; -3,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,11; -3,2</t>
+          <t>-11,31; -3,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-11,4; -3,42</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-14,34; -5,76</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-14,27; -5,77</t>
         </is>
       </c>
     </row>
@@ -1498,37 +1227,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-91,09</t>
+          <t>-4,1</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-4,1</t>
+          <t>-8,63</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-8,63</t>
+          <t>-3,04</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-92,38</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-3,04</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
           <t>-7,79</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>-91,76</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,57</t>
+          <t>-4,54; 0,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,16; -4,17</t>
+          <t>-9,95; -4,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-92,77; -89,27</t>
+          <t>-6,67; -1,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,67; -1,7</t>
+          <t>-11,45; -6,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,36; -5,84</t>
+          <t>-4,9; -1,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-93,81; -90,74</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-4,98; -1,38</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-9,73; -5,93</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-92,92; -90,55</t>
+          <t>-9,85; -5,86</t>
         </is>
       </c>
     </row>
@@ -1604,37 +1303,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-4,44%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-4,44%</t>
+          <t>-9,34%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-9,34%</t>
+          <t>-3,32%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-3,32%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
           <t>-8,49%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 0,63</t>
+          <t>-4,92; 0,77</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,04; -4,66</t>
+          <t>-10,78; -4,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,15; -2,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,12; -1,88</t>
+          <t>-12,24; -6,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-12,27; -6,45</t>
+          <t>-5,32; -1,43</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-5,36; -1,51</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-10,44; -6,47</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-10,67; -6,47</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1370,11 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A19"/>

--- a/data/trans_camb/IP41-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP41-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,69</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-0,93</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-6,28</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,69</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 3,69</t>
+          <t>-6,25; 4,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,84; -0,88</t>
+          <t>-10,61; 1,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 5,09</t>
+          <t>-5,32; 4,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 2,44</t>
+          <t>-11,71; -0,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 3,24</t>
+          <t>-3,73; 3,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,3; -0,71</t>
+          <t>-8,73; -0,69</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-0,6%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-4,02%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-0,98%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-6,61%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,6%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-4,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 3,95</t>
+          <t>-6,65; 5,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,26; -1,0</t>
+          <t>-11,3; 1,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 5,86</t>
+          <t>-5,42; 4,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 2,66</t>
+          <t>-12,12; -1,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 3,56</t>
+          <t>-3,92; 3,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,75; -0,81</t>
+          <t>-9,3; -0,76</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-3,62</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-9,71</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-2,94</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-4,1</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,62</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-9,71</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 1,79</t>
+          <t>-7,5; 0,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 0,66</t>
+          <t>-14,67; -5,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 0,29</t>
+          <t>-7,56; 1,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,37; -4,97</t>
+          <t>-8,76; 0,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,22; -0,25</t>
+          <t>-6,41; -0,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,6; -3,8</t>
+          <t>-10,49; -3,92</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-3,9%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-10,44%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-3,24%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-4,52%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-3,9%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-10,44%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 2,04</t>
+          <t>-7,98; 0,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 0,66</t>
+          <t>-15,49; -5,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 0,28</t>
+          <t>-8,12; 1,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,15; -5,46</t>
+          <t>-9,4; 0,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,71; -0,3</t>
+          <t>-6,9; -0,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,28; -4,16</t>
+          <t>-11,21; -4,3</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-10,64</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>2,77</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-5,93</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,51</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-10,64</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 10,6</t>
+          <t>-8,64; 1,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 1,5</t>
+          <t>-16,35; -5,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 2,0</t>
+          <t>-3,37; 9,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,6; -4,65</t>
+          <t>-13,14; 0,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 3,78</t>
+          <t>-4,95; 3,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,95; -3,82</t>
+          <t>-13,26; -3,98</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-3,8%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-11,54%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>3,24%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-6,95%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-3,8%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-11,54%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 13,19</t>
+          <t>-9,26; 1,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 1,8</t>
+          <t>-17,36; -5,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 2,21</t>
+          <t>-3,83; 11,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,61; -5,24</t>
+          <t>-14,86; 1,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 4,39</t>
+          <t>-5,37; 3,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,3; -4,54</t>
+          <t>-14,64; -4,62</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-8,21</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-8,4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-5,36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-10,23</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-8,21</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-8,4</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,65; -0,7</t>
+          <t>-14,0; -3,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,73; -4,19</t>
+          <t>-14,7; -3,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,85; -3,12</t>
+          <t>-10,37; -0,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,01; -3,02</t>
+          <t>-15,82; -4,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,6; -3,1</t>
+          <t>-10,57; -3,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,37; -5,28</t>
+          <t>-14,0; -5,39</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-8,92%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-9,13%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-5,75%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-10,97%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-8,92%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-9,13%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,25; -0,78</t>
+          <t>-15,06; -3,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,51; -4,41</t>
+          <t>-15,79; -3,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-14,86; -3,48</t>
+          <t>-10,99; -0,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,07; -3,35</t>
+          <t>-16,72; -5,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,31; -3,38</t>
+          <t>-11,41; -3,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,27; -5,77</t>
+          <t>-14,88; -5,9</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-4,1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-8,63</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-1,92</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-6,9</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-4,1</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-8,63</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,7</t>
+          <t>-6,73; -1,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,95; -4,04</t>
+          <t>-11,34; -5,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,67; -1,85</t>
+          <t>-4,59; 0,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,45; -6,14</t>
+          <t>-9,74; -3,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,9; -1,3</t>
+          <t>-5,02; -1,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,85; -5,86</t>
+          <t>-9,82; -5,87</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-4,44%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-9,34%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-2,11%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-7,57%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-4,44%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-9,34%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,77</t>
+          <t>-7,27; -1,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,78; -4,48</t>
+          <t>-12,22; -6,19</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-7,15; -2,01</t>
+          <t>-5,01; 0,77</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,24; -6,73</t>
+          <t>-10,58; -4,37</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,32; -1,43</t>
+          <t>-5,4; -1,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -6,47</t>
+          <t>-10,64; -6,43</t>
         </is>
       </c>
     </row>
